--- a/public/studentimport/student_template.xlsx
+++ b/public/studentimport/student_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\emergingTech\public\studentimport\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sahil\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B5A837-D585-4467-A2C3-027A4F9D32FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B22177-EC44-488A-B076-BC6ABC4463AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{242D047A-525A-49B1-A2B0-D3505FC467FD}"/>
   </bookViews>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>b</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Ravi Barik</t>
   </si>
@@ -47,9 +44,6 @@
     <t>Subrat Barik</t>
   </si>
   <si>
-    <t>23, OKCL, Jaydev Vihar, Bhubaneshwar, 751013</t>
-  </si>
-  <si>
     <t>Male</t>
   </si>
   <si>
@@ -59,22 +53,10 @@
     <t>Gender</t>
   </si>
   <si>
-    <t>Roll Number</t>
-  </si>
-  <si>
-    <t>D.O.B</t>
-  </si>
-  <si>
     <t>Student's Father Name</t>
   </si>
   <si>
     <t>Class</t>
-  </si>
-  <si>
-    <t>Section</t>
-  </si>
-  <si>
-    <t>Full Address</t>
   </si>
 </sst>
 </file>
@@ -118,15 +100,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -463,73 +442,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FEA8AD2-2542-4780-B76A-44A1DF692114}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.6328125" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" customWidth="1"/>
-    <col min="4" max="4" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.26953125" customWidth="1"/>
-    <col min="6" max="6" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.08984375" customWidth="1"/>
-    <col min="8" max="8" width="40.81640625" customWidth="1"/>
+    <col min="2" max="2" width="18.26953125" customWidth="1"/>
+    <col min="3" max="3" width="22.26953125" customWidth="1"/>
+    <col min="4" max="5" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="11.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="11.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
         <v>10</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
-    <row r="2" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2">
-        <v>25523</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="3">
-        <v>38159</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2">
-        <v>10</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>3</v>
-      </c>
+    <row r="3" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="11.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:8" ht="11.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:6" ht="11.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/studentimport/student_template.xlsx
+++ b/public/studentimport/student_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sahil\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B22177-EC44-488A-B076-BC6ABC4463AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB9DC8A-6C40-45CF-9109-A12226A951D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{242D047A-525A-49B1-A2B0-D3505FC467FD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{242D047A-525A-49B1-A2B0-D3505FC467FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,25 +38,25 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t>Ravi Barik</t>
-  </si>
-  <si>
-    <t>Subrat Barik</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
     <t>Student Name</t>
   </si>
   <si>
     <t>Gender</t>
   </si>
   <si>
-    <t>Student's Father Name</t>
-  </si>
-  <si>
     <t>Class</t>
+  </si>
+  <si>
+    <t>Father's Name</t>
+  </si>
+  <si>
+    <t>Date of Birth (DD/MM/YYYY)</t>
+  </si>
+  <si>
+    <t>Mobile No.</t>
+  </si>
+  <si>
+    <t>Roll No</t>
   </si>
 </sst>
 </file>
@@ -100,12 +100,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -442,57 +446,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FEA8AD2-2542-4780-B76A-44A1DF692114}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.26953125" customWidth="1"/>
-    <col min="3" max="3" width="22.26953125" customWidth="1"/>
-    <col min="4" max="5" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.81640625" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="11.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="G1" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>10</v>
-      </c>
+    <row r="2" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:6" ht="11.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:7" ht="11.55" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
